--- a/doc/예상질문모음.xlsx
+++ b/doc/예상질문모음.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\SAP_Straffic260119\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A5790D8-327E-445E-A5DC-3C96FFFB5FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{283512D1-0DB7-4170-8537-71648B393A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="15720" xr2:uid="{7EE03E23-47CB-4F78-976C-EC63B5D6A5BC}"/>
+    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{7EE03E23-47CB-4F78-976C-EC63B5D6A5BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <t>Q1. 데이터 가공 로직의 위치
 "코드를 보면 DB에서 가져온 Y/N 데이터를 화면에 O/X로 보여주기 위해 **formatStatus**라는 함수를 프론트엔드에서 사용하셨습니다.
 이런 데이터 변환을 백엔드(SQL이나 Java)에서 처리해서 보내주는 방법도 있을 텐데, 굳이 프론트엔드에서 처리하도록 구현하신 특별한 이유가 있을까요?"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"로그인 기능을 구현하시면서 '아이디 저장' 기능에는 Cookie를 사용하셨고, 
@@ -47,22 +47,14 @@
 이렇게 두 가지 저장소를 각각 나누어 사용하신 이유가 무엇인가요? 
 또, 유저 정보를 sessionStorage에 저장했을 때 발생할 수 있는 
 보안상 혹은 기능상의 특징은 무엇인지 설명해 주세요."</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"데이터의 성격과 보안 요구 수준에 따라 저장소를 분리했습니다.
 우선 아이디 저장은 사용자 편의를 위한 기능으로, 아이디라는 **'비민감 데이터'**만 저장하기 때문에 브라우저를 종료해도 유지되는 **쿠키(Cookie)**를 사용했습니다. 쿠키는 만료 시간을 길게 설정할 수 있어 재방문 시 사용자 경험을 높이는 데 적합합니다.
 추후에 아이디 저장도 타인이 탈취할 가능성을 배제 할 수 없기 때문에 Secure나 Samsite같은 보안 설정을 추가해볼 예정입니다.
 반면, 로그인 성공 후 유저 정보는 보안이 필요한 **'민감 데이터'**입니다. 이 정보는 로그아웃 시 즉시 파기되어야 하고, 다른 페이지나 기능 접근 권한을 결정하는 기준이 됩니다. 따라서 브라우저 탭을 닫으면 자동으로 삭제되고, 로그아웃 시 clear() 처리가 용이한 **세션 스토리지(sessionStorage)**를 선택하여 보안 노출 위험을 최소화했습니다."</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>로그인 로직을 보면 post요청을 하셨는데 현재 코드는 데이터를 params로
-넘기고 계시네요 보안측면으로 볼때 Query String으로 전달하면 어떤위험이
-발생할까요?
-만약 운영환경에서 서버로그에 사용자의 비밀번호가 평문으로 남는 문제가 
-발생한다면 이 코드를 어떻게 수정하시겠어요?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"네, 질문하신 부분은 저의 코드 미스가 맞습니다. POST 요청을 사용했음에도 데이터를 params 객체에 담아 전달하는 바람에, 결과적으로 GET 방식처럼 URL에 민감한 정보가 노출되는 취약점이 발생했습니다.
@@ -70,7 +62,7 @@
 설정할 것입니다.
 마지막으로 보안을 한 층 더 강화한다면 클라이언트에서 서버로 비밀번호를 보낼 때부터 암호화된 전송구간인 HTTPS라는 것을 적용할 예정입니다. DB가 혹시라도 노출될
 상황을 대비해 헤시함수로 복호화 불가능한 형태로 저장하여 데이터 보안의 취약점을 수정할 예정입니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>"저는 데이터의 원천성과 UI 표현 로직을 분리하는 것을 중요하게 생각했습니다.
@@ -78,76 +70,108 @@
 이렇게 구현하면 두 가지 장점이 있습니다.
 첫째, 백엔드에서 불필요한 문자열 가공 연산을 줄여 서버 부하를 분산할 수 있습니다.
 둘째, 향후 기획이 변경되어 'O/X' 대신 '설치/미설치'라는 텍스트나 별도의 아이콘으로 UI를 변경해야 할 때, 서버 코드 수정 없이 프론트엔드 코드만 수정하면 되므로 유지보수와 확장성 면에서 훨씬 유리하기 때문입니다."</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">제 욕심이 들어간 팀명입니다. 뜻으로는 지하철 편의시설 프로젝트이지만 SAP는 독일의 유명한 전사자원시스템입니다.
 저의 개발자 시절 주로 다뤘던 개발언어가 SAP 입니다. 이번 프로젝트를 기점으로 SAP을 기분 좋게 마무리 하면 좋겠다 라는 뜻으로 지었습니다.
 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>WBS를 제작하여 프로젝트를 진행 하였는데 이슈사항은 없었을까요?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>WBS를 기반으로 프로젝트를 진행하는 과정에서, 초기 계획과 달리 일정이 약 일주일 앞당겨지는 상황이 발생했습니다. 이로 인해 테스트 일정을 부득이하게 넘길 가능성이 있었으나, 소연씨가 일부 업무를 분담해 주면서 테스트 일정을 앞당길 수 있었습니다. 그 결과, 모든 단위 및 통합 테스트를 무사히 완료할 수 있었습니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">
 - 팀명의 뜻이 무엇인가요?
 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1. 시스템 아키텍처 및 데이터 설계 관련 (기술 심화)
 Q1. 오픈 API 데이터를 Python으로 전처리하셨다고 했는데, 데이터의 실시간성과 정합성은 어떻게 보장하나요? (예: 지하철 공사의 데이터가 갱신되었을 때 본 시스템에 어떻게 반영되는지)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>추천 답변: "현재 시스템은 수집된 로우 데이터를 정제하여 DB에 저장하는 방식을 취하고 있습니다. 실시간성을 높이기 위해 스케줄러(예: APScheduler)를 도입하여 주기적으로 API를 호출하고, 데이터가 변경된 경우에만 'Update'를 수행하여 DB 부하를 최소화하면서 최신 정보를 유지하도록 설계했습니다."</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Q2. SQLAlchemy를 사용하셨는데, 복잡한 통계 쿼리를 처리할 때 성능 최적화를 위해 특별히 신경 쓴 부분이 있나요?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>추천 답변: "복잡한 역별 통계나 장애 이력 조회 시 N+1 문제(연관된 데이터를 가져올 때 쿼리가 중복 실행되는 현상)를 방지하기 위해 joinedload나 subqueryload를 활용했습니다. 또한 자주 조회되는 대시보드 데이터는 인덱싱을 통해 조회 속도를 최적화했습니다."</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Q3. 'GitHub의 Pull Request 레이아웃'을 벤치마킹한 것이 인상적입니다. 하지만 IT 비전문가인 현장 관리자가 사용하기에 용어가 생소하거나 구조가 복잡하게 느껴지지는 않을까요?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>중요한 지적입니다. 저희는 레이아웃의 '구조(발생-검토-조치-완료)'만 빌려왔을 뿐, 용어는 '장애 발생', '담당자 확인', '수리 중', '조치 완료'와 같이 현장 친화적인 단어로 변경했습니다. 결과적으로 관리자는 수리 히스토리를 대화형 타임라인으로 확인할 수 있어, 기존 엑셀 방식보다 진행 상황을 훨씬 직관적으로 파악할 수 있습니다."</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Q4. 장애 이슈가 발생했을 때 담당 관리자에게 알림이 가는 기능이 있나요? 없다면 어떤 방식으로 알림 체계를 설계하면 좋을까요?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>추천 답변: "현재는 대시보드 위젯을 통해 실시간 장애 현황을 시각적으로 보여주는 데 집중하고 있습니다. 차후 고도화 단계에서 FastAPI의 WebSocket을 활용한 실시간 브라우저 알림이나, Telegram/Kakao 알림 톡 API를 연동하여 현장 관리자가 즉각적으로 인지할 수 있는 시스템을 추가할 계획입니다."</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Q5. Power BI 리포트에서 '요일별 집중도'를 분석하셨는데, 이 분석 결과가 실제 시설 유지보수 스케줄링(예: 선제적 점검)에 어떻게 활용될 수 있나요?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>추천 답변: "예를 들어 특정 역의 보관함 이용률이 주말에 급증한다는 통계가 있다면, 금요일 오후에 사전 점검 인력을 집중 배치하는 등 '예방 정비' 계획을 세울 수 있습니다. 이는 장애 발생 후 대처하는 '사후 관리' 비용을 획기적으로 줄이는 데이터 기반 경영의 핵심입니다."</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Q6. 만약 이 시스템을 서울뿐만 아니라 다른 지역(부산, 대구 등)의 지하철로 확장한다면, 어떤 부분을 가장 먼저 수정해야 할까요?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>추천 답변: "지역별로 제공하는 오픈 API의 규격(포맷)이 다를 수 있으므로, 데이터 수집 계층을 모듈화하여 각 지역 API에 맞게 어댑터만 교체하면 되도록 설계했습니다. 또한 역별 코드 체계만 DB에 추가하면 시스템 구조 변경 없이 즉시 확장 가능한 유연한 구조를 가지고 있습니다."</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">로그인 로직을 보면 post요청을 하셨는데 현재 코드는 데이터를 params로
+넘기고 계시네요 보안측면으로 볼때 Query String으로 전달하면 어떤위험이
+발생할까요?
+만약 운영환경에서 서버로그에 사용자의 비밀번호가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>평문으로 남는 문제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>가 
+발생한다면 이 코드를 어떻게 수정하시겠어요?</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -164,18 +188,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -206,10 +229,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -526,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3935B96-24C5-4E9A-8E8C-A1E371DBFE67}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="75.796875" customWidth="1"/>
@@ -534,95 +557,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="153" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="176.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="64.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="176.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="139.19999999999999" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="104.4" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="69.599999999999994" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="58.8" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="58.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="2" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="10" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="11" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>21</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>